--- a/src/data/TAHERI_SCOUT_BAND_GROUP_1448H.xlsx
+++ b/src/data/TAHERI_SCOUT_BAND_GROUP_1448H.xlsx
@@ -6,6 +6,8 @@
     <sheet name="Responses" sheetId="1" r:id="rId1"/>
     <sheet name="Member Details" sheetId="2" r:id="rId2"/>
     <sheet name="Attendance Details" sheetId="3" r:id="rId3"/>
+    <sheet name="Lavajam Details" sheetId="4" r:id="rId4"/>
+    <sheet name="Instrument Expenses" sheetId="5" r:id="rId5"/>
   </sheets>
 </workbook>
 </file>
@@ -2799,585 +2801,1158 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D41"/>
+  <dimension ref="A1:C41"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>ITS Number</v>
+        <v>Full Name</v>
       </c>
       <c r="B1" t="str">
-        <v>Member Name</v>
+        <v>22/09/2026</v>
       </c>
       <c r="C1" t="str">
-        <v>Section</v>
-      </c>
-      <c r="D1" t="str">
         <v>23/09/2026</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>40405751</v>
+        <v>BURHANUDDIN ABBASBHAI GULAMALI</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Present</v>
+      </c>
+      <c r="C2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>TAHER SHABBIR SHIKARI</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Absent</v>
+      </c>
+      <c r="C3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>TAHA MAZHARBHAI KUNDAWALA</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Late</v>
+      </c>
+      <c r="C4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>TAHER AKBARBHAI MANDSORWALA</v>
+      </c>
+      <c r="B5" t="str">
+        <v/>
+      </c>
+      <c r="C5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>BURHAN JUZARBHAI KUNDAWALA</v>
+      </c>
+      <c r="B6" t="str">
+        <v/>
+      </c>
+      <c r="C6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>M ISMAIL SH YUSUFBHAI ZOZWALA</v>
+      </c>
+      <c r="B7" t="str">
+        <v/>
+      </c>
+      <c r="C7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>ABBAS BURHANUDDIN BHAI SODAWALA</v>
+      </c>
+      <c r="B8" t="str">
+        <v/>
+      </c>
+      <c r="C8" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>MUFADDAL ABIZARBHAI VALINABU</v>
+      </c>
+      <c r="B9" t="str">
+        <v/>
+      </c>
+      <c r="C9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>HUSAIN JUJARBHAI KUNDAWALA</v>
+      </c>
+      <c r="B10" t="str">
+        <v/>
+      </c>
+      <c r="C10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>ALIASGAR SHABBIRBHAI PARAWALA</v>
+      </c>
+      <c r="B11" t="str">
+        <v/>
+      </c>
+      <c r="C11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>HUSSAIN HANNANBHAI MULLAMITHAWALA</v>
+      </c>
+      <c r="B12" t="str">
+        <v/>
+      </c>
+      <c r="C12" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>ABBAS HUZEFABHAI DHILA WALA</v>
+      </c>
+      <c r="B13" t="str">
+        <v/>
+      </c>
+      <c r="C13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>TAIKHUM BURHANBHAI BHATIYA</v>
+      </c>
+      <c r="B14" t="str">
+        <v/>
+      </c>
+      <c r="C14" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>MOHAMMAD M.SHABBIRBHAI PAHAD</v>
+      </c>
+      <c r="B15" t="str">
+        <v/>
+      </c>
+      <c r="C15" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>HUSAIN ASGARI BHAI KALYANWALA</v>
+      </c>
+      <c r="B16" t="str">
+        <v/>
+      </c>
+      <c r="C16" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>YUNUS AMMAR SELWALA</v>
+      </c>
+      <c r="B17" t="str">
+        <v/>
+      </c>
+      <c r="C17" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>HUSSAIN ISMAILBHAI PITHAPURWALA</v>
+      </c>
+      <c r="B18" t="str">
+        <v/>
+      </c>
+      <c r="C18" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>SHABBIR KUTBIBHAI BHATIYA</v>
+      </c>
+      <c r="B19" t="str">
+        <v/>
+      </c>
+      <c r="C19" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>TAIYAB SAIFUDDINBHAI JHALODWALA</v>
+      </c>
+      <c r="B20" t="str">
+        <v/>
+      </c>
+      <c r="C20" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>QASIM QUTBIBHAI MANDVIWALA</v>
+      </c>
+      <c r="B21" t="str">
+        <v/>
+      </c>
+      <c r="C21" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>BURHANUDDIN SHABBIR BHAI GURIWALA</v>
+      </c>
+      <c r="B22" t="str">
+        <v/>
+      </c>
+      <c r="C22" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>MOIZ SHABBIRBHAI DHILAWALA</v>
+      </c>
+      <c r="B23" t="str">
+        <v/>
+      </c>
+      <c r="C23" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>MOHAMMED YUSUFBHAI DOHADWALA</v>
+      </c>
+      <c r="B24" t="str">
+        <v/>
+      </c>
+      <c r="C24" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>HUSAIN BURHANBHAI KADVALWALA</v>
+      </c>
+      <c r="B25" t="str">
+        <v/>
+      </c>
+      <c r="C25" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>MUSTAFA BHAI TAIZOONBHAI BHAI PIPLAYA</v>
+      </c>
+      <c r="B26" t="str">
+        <v/>
+      </c>
+      <c r="C26" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>MOHAMMAD MUSTAFABHAI GARBADAWALA</v>
+      </c>
+      <c r="B27" t="str">
+        <v/>
+      </c>
+      <c r="C27" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>FAKHRUDDIN ALIHUSAIN BHAI RANAPURWALA</v>
+      </c>
+      <c r="B28" t="str">
+        <v/>
+      </c>
+      <c r="C28" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>MUSTAFA NAJJMUDDI BANGAD WALA</v>
+      </c>
+      <c r="B29" t="str">
+        <v/>
+      </c>
+      <c r="C29" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>BURHANUDDIN TAHER NALAWALA</v>
+      </c>
+      <c r="B30" t="str">
+        <v/>
+      </c>
+      <c r="C30" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>HUSAIN MUSTUFABHAI GHADIYALI</v>
+      </c>
+      <c r="B31" t="str">
+        <v/>
+      </c>
+      <c r="C31" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>HUSAIN KUTBUDDINBHAI KACHERIWALA</v>
+      </c>
+      <c r="B32" t="str">
+        <v/>
+      </c>
+      <c r="C32" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>TAHA BHAI KHOJEMA BHAI ZABUAWALA</v>
+      </c>
+      <c r="B33" t="str">
+        <v/>
+      </c>
+      <c r="C33" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>YUSUF IBRAHIM KAPADIYA</v>
+      </c>
+      <c r="B34" t="str">
+        <v/>
+      </c>
+      <c r="C34" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>MOIZ ALIASGEBHAI PAHADWALA</v>
+      </c>
+      <c r="B35" t="str">
+        <v/>
+      </c>
+      <c r="C35" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>HUZAIFA MUSTAFA CHALLAWALA</v>
+      </c>
+      <c r="B36" t="str">
+        <v/>
+      </c>
+      <c r="C36" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>BURHANUDDIN JUZERBHAI PIPALIYAWALA</v>
+      </c>
+      <c r="B37" t="str">
+        <v/>
+      </c>
+      <c r="C37" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>TAHER SAIFUDDIN BHAI MANGAL MAHUDIWALA</v>
+      </c>
+      <c r="B38" t="str">
+        <v/>
+      </c>
+      <c r="C38" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>MURTUZA MOHAMMAD BHAI MULLAMITHA WALA</v>
+      </c>
+      <c r="B39" t="str">
+        <v/>
+      </c>
+      <c r="C39" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>ALIASGAR MUFADDAL KANCHWALA</v>
+      </c>
+      <c r="B40" t="str">
+        <v/>
+      </c>
+      <c r="C40" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>HUSAIN JUJARBHAI MITHAIWALA</v>
+      </c>
+      <c r="B41" t="str">
+        <v/>
+      </c>
+      <c r="C41" t="str">
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C41"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D45"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Date</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Full Name</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Fund Type</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Amount</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>24/09/2026</v>
       </c>
       <c r="B2" t="str">
         <v>BURHANUDDIN ABBASBHAI GULAMALI</v>
       </c>
       <c r="C2" t="str">
-        <v>SideDrum</v>
-      </c>
-      <c r="D2" t="str">
-        <v>Present</v>
+        <v>Lavajam</v>
+      </c>
+      <c r="D2">
+        <v>1000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>40912151</v>
+        <v>24/09/2026</v>
       </c>
       <c r="B3" t="str">
-        <v>Taher Shabbir Shikari</v>
+        <v>TAHER SHABBIR SHIKARI</v>
       </c>
       <c r="C3" t="str">
-        <v>Trumpet</v>
-      </c>
-      <c r="D3" t="str">
-        <v>Absent</v>
+        <v>Lavajam</v>
+      </c>
+      <c r="D3">
+        <v>1000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>50447649</v>
+        <v>24/09/2026</v>
       </c>
       <c r="B4" t="str">
         <v>TAHA MAZHARBHAI KUNDAWALA</v>
       </c>
       <c r="C4" t="str">
-        <v>SideDrum</v>
-      </c>
-      <c r="D4" t="str">
-        <v>Late</v>
+        <v>Lavajam</v>
+      </c>
+      <c r="D4">
+        <v>1000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>40404863</v>
+        <v>24/09/2026</v>
       </c>
       <c r="B5" t="str">
-        <v>Taher Akbarbhai Mandsorwala</v>
+        <v>TAHER AKBARBHAI MANDSORWALA</v>
       </c>
       <c r="C5" t="str">
-        <v>Trumpet</v>
-      </c>
-      <c r="D5" t="str">
-        <v/>
+        <v>Lavajam</v>
+      </c>
+      <c r="D5">
+        <v>1000</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>40405600</v>
+        <v>24/09/2026</v>
       </c>
       <c r="B6" t="str">
-        <v>Burhan Juzarbhai Kundawala</v>
+        <v>BURHAN JUZARBHAI KUNDAWALA</v>
       </c>
       <c r="C6" t="str">
-        <v>Trumpet</v>
-      </c>
-      <c r="D6" t="str">
-        <v/>
+        <v>Lavajam</v>
+      </c>
+      <c r="D6">
+        <v>1000</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>40408012</v>
+        <v>24/09/2026</v>
       </c>
       <c r="B7" t="str">
-        <v>M Ismail sh yusufbhai zozwala</v>
+        <v>M ISMAIL SH YUSUFBHAI ZOZWALA</v>
       </c>
       <c r="C7" t="str">
-        <v>Trumpet</v>
-      </c>
-      <c r="D7" t="str">
-        <v/>
+        <v>Lavajam</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>40404034</v>
+        <v>24/09/2026</v>
       </c>
       <c r="B8" t="str">
         <v>ABBAS BURHANUDDIN BHAI SODAWALA</v>
       </c>
       <c r="C8" t="str">
-        <v>Euphonium</v>
-      </c>
-      <c r="D8" t="str">
-        <v/>
+        <v>Lavajam</v>
+      </c>
+      <c r="D8">
+        <v>1000</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>40403000</v>
+        <v>24/09/2026</v>
       </c>
       <c r="B9" t="str">
-        <v>Mufaddal Abizarbhai Valinabu</v>
+        <v>MUFADDAL ABIZARBHAI VALINABU</v>
       </c>
       <c r="C9" t="str">
-        <v>Trumpet</v>
-      </c>
-      <c r="D9" t="str">
-        <v/>
+        <v>Lavajam</v>
+      </c>
+      <c r="D9">
+        <v>1000</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>40405101</v>
+        <v>24/09/2026</v>
       </c>
       <c r="B10" t="str">
         <v>HUSAIN JUJARBHAI KUNDAWALA</v>
       </c>
       <c r="C10" t="str">
-        <v>Trumpet</v>
-      </c>
-      <c r="D10" t="str">
-        <v/>
+        <v>Lavajam</v>
+      </c>
+      <c r="D10">
+        <v>1000</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>40409814</v>
+        <v>24/09/2026</v>
       </c>
       <c r="B11" t="str">
         <v>ALIASGAR SHABBIRBHAI PARAWALA</v>
       </c>
       <c r="C11" t="str">
-        <v>Saxophone</v>
-      </c>
-      <c r="D11" t="str">
-        <v/>
+        <v>Lavajam</v>
+      </c>
+      <c r="D11">
+        <v>1000</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>50445270</v>
+        <v>24/09/2026</v>
       </c>
       <c r="B12" t="str">
-        <v>Hussain Hannanbhai mullamithawala</v>
+        <v>HUSSAIN HANNANBHAI MULLAMITHAWALA</v>
       </c>
       <c r="C12" t="str">
-        <v>Trumpet</v>
-      </c>
-      <c r="D12" t="str">
-        <v/>
+        <v>Lavajam</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>40906648</v>
+        <v>24/09/2026</v>
       </c>
       <c r="B13" t="str">
-        <v>Abbas huzefabhai dhila wala</v>
+        <v>ABBAS HUZEFABHAI DHILA WALA</v>
       </c>
       <c r="C13" t="str">
-        <v>Trumpet</v>
-      </c>
-      <c r="D13" t="str">
-        <v/>
+        <v>Lavajam</v>
+      </c>
+      <c r="D13">
+        <v>1000</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>30141323</v>
+        <v>24/09/2026</v>
       </c>
       <c r="B14" t="str">
-        <v>Taikhum Burhanbhai Bhatiya</v>
+        <v>TAIKHUM BURHANBHAI BHATIYA</v>
       </c>
       <c r="C14" t="str">
-        <v>Trumpet</v>
-      </c>
-      <c r="D14" t="str">
-        <v/>
+        <v>Lavajam</v>
+      </c>
+      <c r="D14">
+        <v>1000</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>40408674</v>
+        <v>24/09/2026</v>
       </c>
       <c r="B15" t="str">
-        <v>Mohammad M.shabbirbhai Pahad</v>
+        <v>MOHAMMAD M.SHABBIRBHAI PAHAD</v>
       </c>
       <c r="C15" t="str">
-        <v>Saxophone</v>
-      </c>
-      <c r="D15" t="str">
-        <v/>
+        <v>Lavajam</v>
+      </c>
+      <c r="D15">
+        <v>1000</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>40907710</v>
+        <v>24/09/2026</v>
       </c>
       <c r="B16" t="str">
-        <v>Husain asgari bhai kalyanwala</v>
+        <v>HUSAIN ASGARI BHAI KALYANWALA</v>
       </c>
       <c r="C16" t="str">
-        <v>Trumpet</v>
-      </c>
-      <c r="D16" t="str">
-        <v/>
+        <v>Lavajam</v>
+      </c>
+      <c r="D16">
+        <v>1000</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>40161624</v>
+        <v>24/09/2026</v>
       </c>
       <c r="B17" t="str">
-        <v>Yunus ammar selwala</v>
+        <v>YUNUS AMMAR SELWALA</v>
       </c>
       <c r="C17" t="str">
-        <v>Dish</v>
-      </c>
-      <c r="D17" t="str">
-        <v/>
+        <v>Lavajam</v>
+      </c>
+      <c r="D17">
+        <v>1000</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>40404390</v>
+        <v>24/09/2026</v>
       </c>
       <c r="B18" t="str">
-        <v>Hussain ismailbhai Pithapurwala</v>
+        <v>HUSSAIN ISMAILBHAI PITHAPURWALA</v>
       </c>
       <c r="C18" t="str">
-        <v>Trombone</v>
-      </c>
-      <c r="D18" t="str">
-        <v/>
+        <v>Lavajam</v>
+      </c>
+      <c r="D18">
+        <v>1000</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>60475670</v>
+        <v>24/09/2026</v>
       </c>
       <c r="B19" t="str">
-        <v>Shabbir Kutbibhai Bhatiya</v>
+        <v>SHABBIR KUTBIBHAI BHATIYA</v>
       </c>
       <c r="C19" t="str">
-        <v>Saxophone</v>
-      </c>
-      <c r="D19" t="str">
-        <v/>
+        <v>Lavajam</v>
+      </c>
+      <c r="D19">
+        <v>1000</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>40408001</v>
+        <v>24/09/2026</v>
       </c>
       <c r="B20" t="str">
-        <v>Taiyab saifuddinbhai jhalodwala</v>
+        <v>TAIYAB SAIFUDDINBHAI JHALODWALA</v>
       </c>
       <c r="C20" t="str">
-        <v>Dish</v>
-      </c>
-      <c r="D20" t="str">
-        <v/>
+        <v>Lavajam</v>
+      </c>
+      <c r="D20">
+        <v>1000</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>50482099</v>
+        <v>24/09/2026</v>
       </c>
       <c r="B21" t="str">
-        <v>Qasim qutbibhai mandviwala</v>
+        <v>QASIM QUTBIBHAI MANDVIWALA</v>
       </c>
       <c r="C21" t="str">
-        <v>Trumpet</v>
-      </c>
-      <c r="D21" t="str">
-        <v/>
+        <v>Lavajam</v>
+      </c>
+      <c r="D21">
+        <v>1000</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>30500618</v>
+        <v>24/09/2026</v>
       </c>
       <c r="B22" t="str">
-        <v>Burhanuddin shabbir bhai guriwala</v>
+        <v>BURHANUDDIN SHABBIR BHAI GURIWALA</v>
       </c>
       <c r="C22" t="str">
-        <v>SideDrum</v>
-      </c>
-      <c r="D22" t="str">
-        <v/>
+        <v>Lavajam</v>
+      </c>
+      <c r="D22">
+        <v>1000</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>50445278</v>
+        <v>24/09/2026</v>
       </c>
       <c r="B23" t="str">
         <v>MOIZ SHABBIRBHAI DHILAWALA</v>
       </c>
       <c r="C23" t="str">
-        <v>SideDrum</v>
-      </c>
-      <c r="D23" t="str">
-        <v/>
+        <v>Lavajam</v>
+      </c>
+      <c r="D23">
+        <v>1000</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>50447611</v>
+        <v>24/09/2026</v>
       </c>
       <c r="B24" t="str">
-        <v>Mohammed yusufbhai dohadwala</v>
+        <v>MOHAMMED YUSUFBHAI DOHADWALA</v>
       </c>
       <c r="C24" t="str">
-        <v>SideDrum</v>
-      </c>
-      <c r="D24" t="str">
-        <v/>
+        <v>Lavajam</v>
+      </c>
+      <c r="D24">
+        <v>1000</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>40408855</v>
+        <v>24/09/2026</v>
       </c>
       <c r="B25" t="str">
-        <v>Husain burhanbhai Kadvalwala</v>
+        <v>HUSAIN BURHANBHAI KADVALWALA</v>
       </c>
       <c r="C25" t="str">
-        <v>Trumpet</v>
-      </c>
-      <c r="D25" t="str">
-        <v/>
+        <v>Lavajam</v>
+      </c>
+      <c r="D25">
+        <v>1000</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>40405707</v>
+        <v>24/09/2026</v>
       </c>
       <c r="B26" t="str">
-        <v>Mustafa bhai taizoonbhai bhai piplaya</v>
+        <v>MUSTAFA BHAI TAIZOONBHAI BHAI PIPLAYA</v>
       </c>
       <c r="C26" t="str">
-        <v>Saxophone</v>
-      </c>
-      <c r="D26" t="str">
-        <v/>
+        <v>Lavajam</v>
+      </c>
+      <c r="D26">
+        <v>1000</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>40408097</v>
+        <v>24/09/2026</v>
       </c>
       <c r="B27" t="str">
-        <v>Mohammad mustafabhai garbadawala</v>
+        <v>MOHAMMAD MUSTAFABHAI GARBADAWALA</v>
       </c>
       <c r="C27" t="str">
-        <v>SideDrum</v>
-      </c>
-      <c r="D27" t="str">
-        <v/>
+        <v>Lavajam</v>
+      </c>
+      <c r="D27">
+        <v>1000</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>40910456</v>
+        <v>24/09/2026</v>
       </c>
       <c r="B28" t="str">
-        <v>Fakhruddin Alihusain bhai Ranapurwala</v>
+        <v>FAKHRUDDIN ALIHUSAIN BHAI RANAPURWALA</v>
       </c>
       <c r="C28" t="str">
-        <v>Trumpet</v>
-      </c>
-      <c r="D28" t="str">
-        <v/>
+        <v>Lavajam</v>
+      </c>
+      <c r="D28">
+        <v>1000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>40918708</v>
+        <v>24/09/2026</v>
       </c>
       <c r="B29" t="str">
-        <v>Mustafa najjmuddi bangad wala</v>
+        <v>MUSTAFA NAJJMUDDI BANGAD WALA</v>
       </c>
       <c r="C29" t="str">
-        <v>Euphonium</v>
-      </c>
-      <c r="D29" t="str">
-        <v/>
+        <v>Lavajam</v>
+      </c>
+      <c r="D29">
+        <v>1000</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>40151901</v>
+        <v>24/09/2026</v>
       </c>
       <c r="B30" t="str">
-        <v>Burhanuddin Taher Nalawala</v>
+        <v>BURHANUDDIN TAHER NALAWALA</v>
       </c>
       <c r="C30" t="str">
-        <v>Dish</v>
-      </c>
-      <c r="D30" t="str">
-        <v/>
+        <v>Lavajam</v>
+      </c>
+      <c r="D30">
+        <v>1000</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>30500996</v>
+        <v>24/09/2026</v>
       </c>
       <c r="B31" t="str">
-        <v>Husain Mustufabhai Ghadiyali</v>
+        <v>HUSAIN MUSTUFABHAI GHADIYALI</v>
       </c>
       <c r="C31" t="str">
-        <v>Saxophone</v>
-      </c>
-      <c r="D31" t="str">
-        <v/>
+        <v>Lavajam</v>
+      </c>
+      <c r="D31">
+        <v>1000</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>50447257</v>
+        <v>24/09/2026</v>
       </c>
       <c r="B32" t="str">
-        <v>Husain Kutbuddinbhai Kacheriwala</v>
+        <v>HUSAIN KUTBUDDINBHAI KACHERIWALA</v>
       </c>
       <c r="C32" t="str">
-        <v>Euphonium</v>
-      </c>
-      <c r="D32" t="str">
-        <v/>
+        <v>Lavajam</v>
+      </c>
+      <c r="D32">
+        <v>1000</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>40700011</v>
+        <v>24/09/2026</v>
       </c>
       <c r="B33" t="str">
-        <v>Taha bhai khojema bhai zabuawala</v>
+        <v>TAHA BHAI KHOJEMA BHAI ZABUAWALA</v>
       </c>
       <c r="C33" t="str">
-        <v>Dish</v>
-      </c>
-      <c r="D33" t="str">
-        <v/>
+        <v>Lavajam</v>
+      </c>
+      <c r="D33">
+        <v>1000</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>30117320</v>
+        <v>24/09/2026</v>
       </c>
       <c r="B34" t="str">
-        <v>Yusuf Ibrahim kapadiya</v>
+        <v>YUSUF IBRAHIM KAPADIYA</v>
       </c>
       <c r="C34" t="str">
-        <v>Dish</v>
-      </c>
-      <c r="D34" t="str">
-        <v/>
+        <v>Lavajam</v>
+      </c>
+      <c r="D34">
+        <v>1000</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>40911368</v>
+        <v>24/09/2026</v>
       </c>
       <c r="B35" t="str">
-        <v>Moiz aliasgebhai pahadwala</v>
+        <v>MOIZ ALIASGEBHAI PAHADWALA</v>
       </c>
       <c r="C35" t="str">
-        <v>Trumpet</v>
-      </c>
-      <c r="D35" t="str">
-        <v/>
+        <v>Lavajam</v>
+      </c>
+      <c r="D35">
+        <v>1000</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>40918788</v>
+        <v>24/09/2026</v>
       </c>
       <c r="B36" t="str">
-        <v>Huzaifa mustafa challawala</v>
+        <v>HUZAIFA MUSTAFA CHALLAWALA</v>
       </c>
       <c r="C36" t="str">
-        <v>Dish</v>
-      </c>
-      <c r="D36" t="str">
-        <v/>
+        <v>Lavajam</v>
+      </c>
+      <c r="D36">
+        <v>1000</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>50451051</v>
+        <v>24/09/2026</v>
       </c>
       <c r="B37" t="str">
-        <v>Burhanuddin Juzerbhai Pipaliyawala</v>
+        <v>BURHANUDDIN JUZERBHAI PIPALIYAWALA</v>
       </c>
       <c r="C37" t="str">
-        <v>SideDrum</v>
-      </c>
-      <c r="D37" t="str">
-        <v/>
+        <v>Lavajam</v>
+      </c>
+      <c r="D37">
+        <v>1000</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>40404190</v>
+        <v>24/09/2026</v>
       </c>
       <c r="B38" t="str">
-        <v>Taher Saifuddin Bhai Mangal MahudiWala</v>
+        <v>TAHER SAIFUDDIN BHAI MANGAL MAHUDIWALA</v>
       </c>
       <c r="C38" t="str">
-        <v>Trumpet</v>
-      </c>
-      <c r="D38" t="str">
-        <v/>
+        <v>Lavajam</v>
+      </c>
+      <c r="D38">
+        <v>1000</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>40155199</v>
+        <v>24/09/2026</v>
       </c>
       <c r="B39" t="str">
-        <v>Murtuza mohammad bhai mullamitha wala</v>
+        <v>MURTUZA MOHAMMAD BHAI MULLAMITHA WALA</v>
       </c>
       <c r="C39" t="str">
-        <v>Trumpet</v>
-      </c>
-      <c r="D39" t="str">
-        <v/>
+        <v>Lavajam</v>
+      </c>
+      <c r="D39">
+        <v>1000</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>40915293</v>
+        <v>24/09/2026</v>
       </c>
       <c r="B40" t="str">
-        <v>Aliasgar mufaddal kanchwala</v>
+        <v>ALIASGAR MUFADDAL KANCHWALA</v>
       </c>
       <c r="C40" t="str">
-        <v>Trumpet</v>
-      </c>
-      <c r="D40" t="str">
-        <v/>
+        <v>Lavajam</v>
+      </c>
+      <c r="D40">
+        <v>1000</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>30710810</v>
+        <v>24/09/2026</v>
       </c>
       <c r="B41" t="str">
-        <v>Husain Jujarbhai Mithaiwala</v>
+        <v>HUSAIN JUJARBHAI MITHAIWALA</v>
       </c>
       <c r="C41" t="str">
-        <v>Euphonium</v>
-      </c>
-      <c r="D41" t="str">
-        <v/>
+        <v>Lavajam</v>
+      </c>
+      <c r="D41">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>24/09/2026</v>
+      </c>
+      <c r="B42" t="str">
+        <v>Mohammad bhai jiruwala</v>
+      </c>
+      <c r="C42" t="str">
+        <v xml:space="preserve">HOOB </v>
+      </c>
+      <c r="D42">
+        <v>5253</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>24/09/2026</v>
+      </c>
+      <c r="B43" t="str">
+        <v>Aliasgar happawala</v>
+      </c>
+      <c r="C43" t="str">
+        <v xml:space="preserve">HOOB </v>
+      </c>
+      <c r="D43">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>24/09/2026</v>
+      </c>
+      <c r="B44" t="str">
+        <v xml:space="preserve">Hozefa bhai kagdi </v>
+      </c>
+      <c r="C44" t="str">
+        <v xml:space="preserve">HOOB </v>
+      </c>
+      <c r="D44">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>24/09/2026</v>
+      </c>
+      <c r="B45" t="str">
+        <v>Hatim bhai gulgula</v>
+      </c>
+      <c r="C45" t="str">
+        <v xml:space="preserve">HOOB </v>
+      </c>
+      <c r="D45">
+        <v>10000</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D41"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D45"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C4"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Date</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Expense Details</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Amount</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>24/09/2026</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Instument purchase</v>
+      </c>
+      <c r="C2">
+        <v>20500</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>24/09/2026</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Baner express</v>
+      </c>
+      <c r="C3">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>24/09/2026</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Instument purchase</v>
+      </c>
+      <c r="C4">
+        <v>1370</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C4"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/src/data/TAHERI_SCOUT_BAND_GROUP_1448H.xlsx
+++ b/src/data/TAHERI_SCOUT_BAND_GROUP_1448H.xlsx
@@ -3263,641 +3263,506 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D45"/>
+  <dimension ref="A1:C45"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>Date</v>
+        <v>Full Name</v>
       </c>
       <c r="B1" t="str">
-        <v>Full Name</v>
+        <v>Fund Type</v>
       </c>
       <c r="C1" t="str">
-        <v>Fund Type</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Amount</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>24/09/2026</v>
+        <v>BURHANUDDIN ABBASBHAI GULAMALI</v>
       </c>
       <c r="B2" t="str">
-        <v>BURHANUDDIN ABBASBHAI GULAMALI</v>
-      </c>
-      <c r="C2" t="str">
         <v>Lavajam</v>
       </c>
-      <c r="D2">
+      <c r="C2">
         <v>1000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>24/09/2026</v>
+        <v>TAHER SHABBIR SHIKARI</v>
       </c>
       <c r="B3" t="str">
-        <v>TAHER SHABBIR SHIKARI</v>
-      </c>
-      <c r="C3" t="str">
         <v>Lavajam</v>
       </c>
-      <c r="D3">
+      <c r="C3">
         <v>1000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>24/09/2026</v>
+        <v>TAHA MAZHARBHAI KUNDAWALA</v>
       </c>
       <c r="B4" t="str">
-        <v>TAHA MAZHARBHAI KUNDAWALA</v>
-      </c>
-      <c r="C4" t="str">
         <v>Lavajam</v>
       </c>
-      <c r="D4">
+      <c r="C4">
         <v>1000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>24/09/2026</v>
+        <v>TAHER AKBARBHAI MANDSORWALA</v>
       </c>
       <c r="B5" t="str">
-        <v>TAHER AKBARBHAI MANDSORWALA</v>
-      </c>
-      <c r="C5" t="str">
         <v>Lavajam</v>
       </c>
-      <c r="D5">
+      <c r="C5">
         <v>1000</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>24/09/2026</v>
+        <v>BURHAN JUZARBHAI KUNDAWALA</v>
       </c>
       <c r="B6" t="str">
-        <v>BURHAN JUZARBHAI KUNDAWALA</v>
-      </c>
-      <c r="C6" t="str">
         <v>Lavajam</v>
       </c>
-      <c r="D6">
+      <c r="C6">
         <v>1000</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>24/09/2026</v>
+        <v>M ISMAIL SH YUSUFBHAI ZOZWALA</v>
       </c>
       <c r="B7" t="str">
-        <v>M ISMAIL SH YUSUFBHAI ZOZWALA</v>
+        <v/>
       </c>
       <c r="C7" t="str">
-        <v>Lavajam</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>24/09/2026</v>
+        <v>ABBAS BURHANUDDIN BHAI SODAWALA</v>
       </c>
       <c r="B8" t="str">
-        <v>ABBAS BURHANUDDIN BHAI SODAWALA</v>
-      </c>
-      <c r="C8" t="str">
         <v>Lavajam</v>
       </c>
-      <c r="D8">
+      <c r="C8">
         <v>1000</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>24/09/2026</v>
+        <v>MUFADDAL ABIZARBHAI VALINABU</v>
       </c>
       <c r="B9" t="str">
-        <v>MUFADDAL ABIZARBHAI VALINABU</v>
-      </c>
-      <c r="C9" t="str">
         <v>Lavajam</v>
       </c>
-      <c r="D9">
+      <c r="C9">
         <v>1000</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>24/09/2026</v>
+        <v>HUSAIN JUJARBHAI KUNDAWALA</v>
       </c>
       <c r="B10" t="str">
-        <v>HUSAIN JUJARBHAI KUNDAWALA</v>
-      </c>
-      <c r="C10" t="str">
         <v>Lavajam</v>
       </c>
-      <c r="D10">
+      <c r="C10">
         <v>1000</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>24/09/2026</v>
+        <v>ALIASGAR SHABBIRBHAI PARAWALA</v>
       </c>
       <c r="B11" t="str">
-        <v>ALIASGAR SHABBIRBHAI PARAWALA</v>
-      </c>
-      <c r="C11" t="str">
         <v>Lavajam</v>
       </c>
-      <c r="D11">
+      <c r="C11">
         <v>1000</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>24/09/2026</v>
+        <v>HUSSAIN HANNANBHAI MULLAMITHAWALA</v>
       </c>
       <c r="B12" t="str">
-        <v>HUSSAIN HANNANBHAI MULLAMITHAWALA</v>
+        <v/>
       </c>
       <c r="C12" t="str">
-        <v>Lavajam</v>
-      </c>
-      <c r="D12">
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>24/09/2026</v>
+        <v>ABBAS HUZEFABHAI DHILA WALA</v>
       </c>
       <c r="B13" t="str">
-        <v>ABBAS HUZEFABHAI DHILA WALA</v>
-      </c>
-      <c r="C13" t="str">
         <v>Lavajam</v>
       </c>
-      <c r="D13">
+      <c r="C13">
         <v>1000</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>24/09/2026</v>
+        <v>TAIKHUM BURHANBHAI BHATIYA</v>
       </c>
       <c r="B14" t="str">
-        <v>TAIKHUM BURHANBHAI BHATIYA</v>
-      </c>
-      <c r="C14" t="str">
         <v>Lavajam</v>
       </c>
-      <c r="D14">
+      <c r="C14">
         <v>1000</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>24/09/2026</v>
+        <v>MOHAMMAD M.SHABBIRBHAI PAHAD</v>
       </c>
       <c r="B15" t="str">
-        <v>MOHAMMAD M.SHABBIRBHAI PAHAD</v>
-      </c>
-      <c r="C15" t="str">
         <v>Lavajam</v>
       </c>
-      <c r="D15">
+      <c r="C15">
         <v>1000</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>24/09/2026</v>
+        <v>HUSAIN ASGARI BHAI KALYANWALA</v>
       </c>
       <c r="B16" t="str">
-        <v>HUSAIN ASGARI BHAI KALYANWALA</v>
-      </c>
-      <c r="C16" t="str">
         <v>Lavajam</v>
       </c>
-      <c r="D16">
+      <c r="C16">
         <v>1000</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>24/09/2026</v>
+        <v>YUNUS AMMAR SELWALA</v>
       </c>
       <c r="B17" t="str">
-        <v>YUNUS AMMAR SELWALA</v>
-      </c>
-      <c r="C17" t="str">
         <v>Lavajam</v>
       </c>
-      <c r="D17">
+      <c r="C17">
         <v>1000</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>24/09/2026</v>
+        <v>HUSSAIN ISMAILBHAI PITHAPURWALA</v>
       </c>
       <c r="B18" t="str">
-        <v>HUSSAIN ISMAILBHAI PITHAPURWALA</v>
-      </c>
-      <c r="C18" t="str">
         <v>Lavajam</v>
       </c>
-      <c r="D18">
+      <c r="C18">
         <v>1000</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>24/09/2026</v>
+        <v>SHABBIR KUTBIBHAI BHATIYA</v>
       </c>
       <c r="B19" t="str">
-        <v>SHABBIR KUTBIBHAI BHATIYA</v>
-      </c>
-      <c r="C19" t="str">
         <v>Lavajam</v>
       </c>
-      <c r="D19">
+      <c r="C19">
         <v>1000</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>24/09/2026</v>
+        <v>TAIYAB SAIFUDDINBHAI JHALODWALA</v>
       </c>
       <c r="B20" t="str">
-        <v>TAIYAB SAIFUDDINBHAI JHALODWALA</v>
-      </c>
-      <c r="C20" t="str">
         <v>Lavajam</v>
       </c>
-      <c r="D20">
+      <c r="C20">
         <v>1000</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>24/09/2026</v>
+        <v>QASIM QUTBIBHAI MANDVIWALA</v>
       </c>
       <c r="B21" t="str">
-        <v>QASIM QUTBIBHAI MANDVIWALA</v>
-      </c>
-      <c r="C21" t="str">
         <v>Lavajam</v>
       </c>
-      <c r="D21">
+      <c r="C21">
         <v>1000</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>24/09/2026</v>
+        <v>BURHANUDDIN SHABBIR BHAI GURIWALA</v>
       </c>
       <c r="B22" t="str">
-        <v>BURHANUDDIN SHABBIR BHAI GURIWALA</v>
-      </c>
-      <c r="C22" t="str">
         <v>Lavajam</v>
       </c>
-      <c r="D22">
+      <c r="C22">
         <v>1000</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>24/09/2026</v>
+        <v>MOIZ SHABBIRBHAI DHILAWALA</v>
       </c>
       <c r="B23" t="str">
-        <v>MOIZ SHABBIRBHAI DHILAWALA</v>
-      </c>
-      <c r="C23" t="str">
         <v>Lavajam</v>
       </c>
-      <c r="D23">
+      <c r="C23">
         <v>1000</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>24/09/2026</v>
+        <v>MOHAMMED YUSUFBHAI DOHADWALA</v>
       </c>
       <c r="B24" t="str">
-        <v>MOHAMMED YUSUFBHAI DOHADWALA</v>
-      </c>
-      <c r="C24" t="str">
         <v>Lavajam</v>
       </c>
-      <c r="D24">
+      <c r="C24">
         <v>1000</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>24/09/2026</v>
+        <v>HUSAIN BURHANBHAI KADVALWALA</v>
       </c>
       <c r="B25" t="str">
-        <v>HUSAIN BURHANBHAI KADVALWALA</v>
-      </c>
-      <c r="C25" t="str">
         <v>Lavajam</v>
       </c>
-      <c r="D25">
+      <c r="C25">
         <v>1000</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>24/09/2026</v>
+        <v>MUSTAFA BHAI TAIZOONBHAI BHAI PIPLAYA</v>
       </c>
       <c r="B26" t="str">
-        <v>MUSTAFA BHAI TAIZOONBHAI BHAI PIPLAYA</v>
-      </c>
-      <c r="C26" t="str">
         <v>Lavajam</v>
       </c>
-      <c r="D26">
+      <c r="C26">
         <v>1000</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>24/09/2026</v>
+        <v>MOHAMMAD MUSTAFABHAI GARBADAWALA</v>
       </c>
       <c r="B27" t="str">
-        <v>MOHAMMAD MUSTAFABHAI GARBADAWALA</v>
-      </c>
-      <c r="C27" t="str">
         <v>Lavajam</v>
       </c>
-      <c r="D27">
+      <c r="C27">
         <v>1000</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>24/09/2026</v>
+        <v>FAKHRUDDIN ALIHUSAIN BHAI RANAPURWALA</v>
       </c>
       <c r="B28" t="str">
-        <v>FAKHRUDDIN ALIHUSAIN BHAI RANAPURWALA</v>
-      </c>
-      <c r="C28" t="str">
         <v>Lavajam</v>
       </c>
-      <c r="D28">
+      <c r="C28">
         <v>1000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>24/09/2026</v>
+        <v>MUSTAFA NAJJMUDDI BANGAD WALA</v>
       </c>
       <c r="B29" t="str">
-        <v>MUSTAFA NAJJMUDDI BANGAD WALA</v>
-      </c>
-      <c r="C29" t="str">
         <v>Lavajam</v>
       </c>
-      <c r="D29">
+      <c r="C29">
         <v>1000</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>24/09/2026</v>
+        <v>BURHANUDDIN TAHER NALAWALA</v>
       </c>
       <c r="B30" t="str">
-        <v>BURHANUDDIN TAHER NALAWALA</v>
-      </c>
-      <c r="C30" t="str">
         <v>Lavajam</v>
       </c>
-      <c r="D30">
+      <c r="C30">
         <v>1000</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>24/09/2026</v>
+        <v>HUSAIN MUSTUFABHAI GHADIYALI</v>
       </c>
       <c r="B31" t="str">
-        <v>HUSAIN MUSTUFABHAI GHADIYALI</v>
-      </c>
-      <c r="C31" t="str">
         <v>Lavajam</v>
       </c>
-      <c r="D31">
+      <c r="C31">
         <v>1000</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>24/09/2026</v>
+        <v>HUSAIN KUTBUDDINBHAI KACHERIWALA</v>
       </c>
       <c r="B32" t="str">
-        <v>HUSAIN KUTBUDDINBHAI KACHERIWALA</v>
-      </c>
-      <c r="C32" t="str">
         <v>Lavajam</v>
       </c>
-      <c r="D32">
+      <c r="C32">
         <v>1000</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>24/09/2026</v>
+        <v>TAHA BHAI KHOJEMA BHAI ZABUAWALA</v>
       </c>
       <c r="B33" t="str">
-        <v>TAHA BHAI KHOJEMA BHAI ZABUAWALA</v>
-      </c>
-      <c r="C33" t="str">
         <v>Lavajam</v>
       </c>
-      <c r="D33">
+      <c r="C33">
         <v>1000</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>24/09/2026</v>
+        <v>YUSUF IBRAHIM KAPADIYA</v>
       </c>
       <c r="B34" t="str">
-        <v>YUSUF IBRAHIM KAPADIYA</v>
-      </c>
-      <c r="C34" t="str">
         <v>Lavajam</v>
       </c>
-      <c r="D34">
+      <c r="C34">
         <v>1000</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>24/09/2026</v>
+        <v>MOIZ ALIASGEBHAI PAHADWALA</v>
       </c>
       <c r="B35" t="str">
-        <v>MOIZ ALIASGEBHAI PAHADWALA</v>
-      </c>
-      <c r="C35" t="str">
         <v>Lavajam</v>
       </c>
-      <c r="D35">
+      <c r="C35">
         <v>1000</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>24/09/2026</v>
+        <v>HUZAIFA MUSTAFA CHALLAWALA</v>
       </c>
       <c r="B36" t="str">
-        <v>HUZAIFA MUSTAFA CHALLAWALA</v>
-      </c>
-      <c r="C36" t="str">
         <v>Lavajam</v>
       </c>
-      <c r="D36">
+      <c r="C36">
         <v>1000</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>24/09/2026</v>
+        <v>BURHANUDDIN JUZERBHAI PIPALIYAWALA</v>
       </c>
       <c r="B37" t="str">
-        <v>BURHANUDDIN JUZERBHAI PIPALIYAWALA</v>
-      </c>
-      <c r="C37" t="str">
         <v>Lavajam</v>
       </c>
-      <c r="D37">
+      <c r="C37">
         <v>1000</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>24/09/2026</v>
+        <v>TAHER SAIFUDDIN BHAI MANGAL MAHUDIWALA</v>
       </c>
       <c r="B38" t="str">
-        <v>TAHER SAIFUDDIN BHAI MANGAL MAHUDIWALA</v>
-      </c>
-      <c r="C38" t="str">
         <v>Lavajam</v>
       </c>
-      <c r="D38">
+      <c r="C38">
         <v>1000</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>24/09/2026</v>
+        <v>MURTUZA MOHAMMAD BHAI MULLAMITHA WALA</v>
       </c>
       <c r="B39" t="str">
-        <v>MURTUZA MOHAMMAD BHAI MULLAMITHA WALA</v>
-      </c>
-      <c r="C39" t="str">
         <v>Lavajam</v>
       </c>
-      <c r="D39">
+      <c r="C39">
         <v>1000</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>24/09/2026</v>
+        <v>ALIASGAR MUFADDAL KANCHWALA</v>
       </c>
       <c r="B40" t="str">
-        <v>ALIASGAR MUFADDAL KANCHWALA</v>
-      </c>
-      <c r="C40" t="str">
         <v>Lavajam</v>
       </c>
-      <c r="D40">
+      <c r="C40">
         <v>1000</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>24/09/2026</v>
+        <v>HUSAIN JUJARBHAI MITHAIWALA</v>
       </c>
       <c r="B41" t="str">
-        <v>HUSAIN JUJARBHAI MITHAIWALA</v>
-      </c>
-      <c r="C41" t="str">
         <v>Lavajam</v>
       </c>
-      <c r="D41">
+      <c r="C41">
         <v>1000</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>24/09/2026</v>
+        <v>Mohammad bhai jiruwala</v>
       </c>
       <c r="B42" t="str">
-        <v>Mohammad bhai jiruwala</v>
-      </c>
-      <c r="C42" t="str">
-        <v xml:space="preserve">HOOB </v>
-      </c>
-      <c r="D42">
+        <v>HOOB</v>
+      </c>
+      <c r="C42">
         <v>5253</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>24/09/2026</v>
+        <v>Aliasgar happawala</v>
       </c>
       <c r="B43" t="str">
-        <v>Aliasgar happawala</v>
-      </c>
-      <c r="C43" t="str">
-        <v xml:space="preserve">HOOB </v>
-      </c>
-      <c r="D43">
+        <v>HOOB</v>
+      </c>
+      <c r="C43">
         <v>6000</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>24/09/2026</v>
+        <v>Hozefa bhai kagdi</v>
       </c>
       <c r="B44" t="str">
-        <v xml:space="preserve">Hozefa bhai kagdi </v>
-      </c>
-      <c r="C44" t="str">
-        <v xml:space="preserve">HOOB </v>
-      </c>
-      <c r="D44">
+        <v>HOOB</v>
+      </c>
+      <c r="C44">
         <v>8000</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>24/09/2026</v>
+        <v>Hatim bhai gulgula</v>
       </c>
       <c r="B45" t="str">
-        <v>Hatim bhai gulgula</v>
-      </c>
-      <c r="C45" t="str">
-        <v xml:space="preserve">HOOB </v>
-      </c>
-      <c r="D45">
+        <v>HOOB</v>
+      </c>
+      <c r="C45">
         <v>10000</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D45"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C45"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/src/data/TAHERI_SCOUT_BAND_GROUP_1448H.xlsx
+++ b/src/data/TAHERI_SCOUT_BAND_GROUP_1448H.xlsx
@@ -3263,7 +3263,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C45"/>
+  <dimension ref="A1:C43"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3333,18 +3333,18 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>M ISMAIL SH YUSUFBHAI ZOZWALA</v>
+        <v>ABBAS BURHANUDDIN BHAI SODAWALA</v>
       </c>
       <c r="B7" t="str">
-        <v/>
-      </c>
-      <c r="C7" t="str">
-        <v/>
+        <v>Lavajam</v>
+      </c>
+      <c r="C7">
+        <v>1000</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>ABBAS BURHANUDDIN BHAI SODAWALA</v>
+        <v>MUFADDAL ABIZARBHAI VALINABU</v>
       </c>
       <c r="B8" t="str">
         <v>Lavajam</v>
@@ -3355,7 +3355,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>MUFADDAL ABIZARBHAI VALINABU</v>
+        <v>HUSAIN JUJARBHAI KUNDAWALA</v>
       </c>
       <c r="B9" t="str">
         <v>Lavajam</v>
@@ -3366,7 +3366,7 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>HUSAIN JUJARBHAI KUNDAWALA</v>
+        <v>ALIASGAR SHABBIRBHAI PARAWALA</v>
       </c>
       <c r="B10" t="str">
         <v>Lavajam</v>
@@ -3377,7 +3377,7 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>ALIASGAR SHABBIRBHAI PARAWALA</v>
+        <v>ABBAS HUZEFABHAI DHILA WALA</v>
       </c>
       <c r="B11" t="str">
         <v>Lavajam</v>
@@ -3388,18 +3388,18 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>HUSSAIN HANNANBHAI MULLAMITHAWALA</v>
+        <v>TAIKHUM BURHANBHAI BHATIYA</v>
       </c>
       <c r="B12" t="str">
-        <v/>
-      </c>
-      <c r="C12" t="str">
-        <v/>
+        <v>Lavajam</v>
+      </c>
+      <c r="C12">
+        <v>1000</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>ABBAS HUZEFABHAI DHILA WALA</v>
+        <v>MOHAMMAD M.SHABBIRBHAI PAHAD</v>
       </c>
       <c r="B13" t="str">
         <v>Lavajam</v>
@@ -3410,7 +3410,7 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>TAIKHUM BURHANBHAI BHATIYA</v>
+        <v>HUSAIN ASGARI BHAI KALYANWALA</v>
       </c>
       <c r="B14" t="str">
         <v>Lavajam</v>
@@ -3421,7 +3421,7 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>MOHAMMAD M.SHABBIRBHAI PAHAD</v>
+        <v>YUNUS AMMAR SELWALA</v>
       </c>
       <c r="B15" t="str">
         <v>Lavajam</v>
@@ -3432,7 +3432,7 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>HUSAIN ASGARI BHAI KALYANWALA</v>
+        <v>HUSSAIN ISMAILBHAI PITHAPURWALA</v>
       </c>
       <c r="B16" t="str">
         <v>Lavajam</v>
@@ -3443,7 +3443,7 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>YUNUS AMMAR SELWALA</v>
+        <v>SHABBIR KUTBIBHAI BHATIYA</v>
       </c>
       <c r="B17" t="str">
         <v>Lavajam</v>
@@ -3454,7 +3454,7 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>HUSSAIN ISMAILBHAI PITHAPURWALA</v>
+        <v>TAIYAB SAIFUDDINBHAI JHALODWALA</v>
       </c>
       <c r="B18" t="str">
         <v>Lavajam</v>
@@ -3465,7 +3465,7 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>SHABBIR KUTBIBHAI BHATIYA</v>
+        <v>QASIM QUTBIBHAI MANDVIWALA</v>
       </c>
       <c r="B19" t="str">
         <v>Lavajam</v>
@@ -3476,7 +3476,7 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>TAIYAB SAIFUDDINBHAI JHALODWALA</v>
+        <v>BURHANUDDIN SHABBIR BHAI GURIWALA</v>
       </c>
       <c r="B20" t="str">
         <v>Lavajam</v>
@@ -3487,7 +3487,7 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>QASIM QUTBIBHAI MANDVIWALA</v>
+        <v>MOIZ SHABBIRBHAI DHILAWALA</v>
       </c>
       <c r="B21" t="str">
         <v>Lavajam</v>
@@ -3498,7 +3498,7 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>BURHANUDDIN SHABBIR BHAI GURIWALA</v>
+        <v>MOHAMMED YUSUFBHAI DOHADWALA</v>
       </c>
       <c r="B22" t="str">
         <v>Lavajam</v>
@@ -3509,7 +3509,7 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>MOIZ SHABBIRBHAI DHILAWALA</v>
+        <v>HUSAIN BURHANBHAI KADVALWALA</v>
       </c>
       <c r="B23" t="str">
         <v>Lavajam</v>
@@ -3520,7 +3520,7 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>MOHAMMED YUSUFBHAI DOHADWALA</v>
+        <v>MUSTAFA BHAI TAIZOONBHAI BHAI PIPLAYA</v>
       </c>
       <c r="B24" t="str">
         <v>Lavajam</v>
@@ -3531,7 +3531,7 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>HUSAIN BURHANBHAI KADVALWALA</v>
+        <v>MOHAMMAD MUSTAFABHAI GARBADAWALA</v>
       </c>
       <c r="B25" t="str">
         <v>Lavajam</v>
@@ -3542,7 +3542,7 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>MUSTAFA BHAI TAIZOONBHAI BHAI PIPLAYA</v>
+        <v>FAKHRUDDIN ALIHUSAIN BHAI RANAPURWALA</v>
       </c>
       <c r="B26" t="str">
         <v>Lavajam</v>
@@ -3553,7 +3553,7 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>MOHAMMAD MUSTAFABHAI GARBADAWALA</v>
+        <v>MUSTAFA NAJJMUDDI BANGAD WALA</v>
       </c>
       <c r="B27" t="str">
         <v>Lavajam</v>
@@ -3564,7 +3564,7 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>FAKHRUDDIN ALIHUSAIN BHAI RANAPURWALA</v>
+        <v>BURHANUDDIN TAHER NALAWALA</v>
       </c>
       <c r="B28" t="str">
         <v>Lavajam</v>
@@ -3575,7 +3575,7 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>MUSTAFA NAJJMUDDI BANGAD WALA</v>
+        <v>HUSAIN MUSTUFABHAI GHADIYALI</v>
       </c>
       <c r="B29" t="str">
         <v>Lavajam</v>
@@ -3586,7 +3586,7 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>BURHANUDDIN TAHER NALAWALA</v>
+        <v>HUSAIN KUTBUDDINBHAI KACHERIWALA</v>
       </c>
       <c r="B30" t="str">
         <v>Lavajam</v>
@@ -3597,7 +3597,7 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>HUSAIN MUSTUFABHAI GHADIYALI</v>
+        <v>TAHA BHAI KHOJEMA BHAI ZABUAWALA</v>
       </c>
       <c r="B31" t="str">
         <v>Lavajam</v>
@@ -3608,7 +3608,7 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>HUSAIN KUTBUDDINBHAI KACHERIWALA</v>
+        <v>YUSUF IBRAHIM KAPADIYA</v>
       </c>
       <c r="B32" t="str">
         <v>Lavajam</v>
@@ -3619,7 +3619,7 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>TAHA BHAI KHOJEMA BHAI ZABUAWALA</v>
+        <v>MOIZ ALIASGEBHAI PAHADWALA</v>
       </c>
       <c r="B33" t="str">
         <v>Lavajam</v>
@@ -3630,7 +3630,7 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>YUSUF IBRAHIM KAPADIYA</v>
+        <v>HUZAIFA MUSTAFA CHALLAWALA</v>
       </c>
       <c r="B34" t="str">
         <v>Lavajam</v>
@@ -3641,7 +3641,7 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>MOIZ ALIASGEBHAI PAHADWALA</v>
+        <v>BURHANUDDIN JUZERBHAI PIPALIYAWALA</v>
       </c>
       <c r="B35" t="str">
         <v>Lavajam</v>
@@ -3652,7 +3652,7 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>HUZAIFA MUSTAFA CHALLAWALA</v>
+        <v>TAHER SAIFUDDIN BHAI MANGAL MAHUDIWALA</v>
       </c>
       <c r="B36" t="str">
         <v>Lavajam</v>
@@ -3663,7 +3663,7 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>BURHANUDDIN JUZERBHAI PIPALIYAWALA</v>
+        <v>MURTUZA MOHAMMAD BHAI MULLAMITHA WALA</v>
       </c>
       <c r="B37" t="str">
         <v>Lavajam</v>
@@ -3674,7 +3674,7 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>TAHER SAIFUDDIN BHAI MANGAL MAHUDIWALA</v>
+        <v>ALIASGAR MUFADDAL KANCHWALA</v>
       </c>
       <c r="B38" t="str">
         <v>Lavajam</v>
@@ -3685,7 +3685,7 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>MURTUZA MOHAMMAD BHAI MULLAMITHA WALA</v>
+        <v>HUSAIN JUJARBHAI MITHAIWALA</v>
       </c>
       <c r="B39" t="str">
         <v>Lavajam</v>
@@ -3696,73 +3696,51 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>ALIASGAR MUFADDAL KANCHWALA</v>
+        <v>Mohammad bhai jiruwala</v>
       </c>
       <c r="B40" t="str">
-        <v>Lavajam</v>
+        <v>HOOB</v>
       </c>
       <c r="C40">
-        <v>1000</v>
+        <v>5253</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>HUSAIN JUJARBHAI MITHAIWALA</v>
+        <v>Aliasgar happawala</v>
       </c>
       <c r="B41" t="str">
-        <v>Lavajam</v>
+        <v>HOOB</v>
       </c>
       <c r="C41">
-        <v>1000</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Mohammad bhai jiruwala</v>
+        <v>Hozefa bhai kagdi</v>
       </c>
       <c r="B42" t="str">
         <v>HOOB</v>
       </c>
       <c r="C42">
-        <v>5253</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Aliasgar happawala</v>
+        <v>Hatim bhai gulgula</v>
       </c>
       <c r="B43" t="str">
         <v>HOOB</v>
       </c>
       <c r="C43">
-        <v>6000</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="str">
-        <v>Hozefa bhai kagdi</v>
-      </c>
-      <c r="B44" t="str">
-        <v>HOOB</v>
-      </c>
-      <c r="C44">
-        <v>8000</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="str">
-        <v>Hatim bhai gulgula</v>
-      </c>
-      <c r="B45" t="str">
-        <v>HOOB</v>
-      </c>
-      <c r="C45">
         <v>10000</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C45"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C43"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/src/data/TAHERI_SCOUT_BAND_GROUP_1448H.xlsx
+++ b/src/data/TAHERI_SCOUT_BAND_GROUP_1448H.xlsx
@@ -8,6 +8,7 @@
     <sheet name="Attendance Details" sheetId="3" r:id="rId3"/>
     <sheet name="Lavajam Details" sheetId="4" r:id="rId4"/>
     <sheet name="Instrument Expenses" sheetId="5" r:id="rId5"/>
+    <sheet name="Reference Link" sheetId="6" r:id="rId6"/>
   </sheets>
 </workbook>
 </file>
@@ -3798,4 +3799,73 @@
     <ignoredError numberStoredAsText="1" sqref="A1:C4"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I2"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Timestamp</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Tune Name</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Instrument Type</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Target Drive Folder</v>
+      </c>
+      <c r="E1" t="str">
+        <v>File Name</v>
+      </c>
+      <c r="F1" t="str">
+        <v>File URL</v>
+      </c>
+      <c r="G1" t="str">
+        <v>YouTube Link</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Instagram Link</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Uploaded By</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>2026-09-25T20:06:57.662Z</v>
+      </c>
+      <c r="B2" t="str">
+        <v>burhandeen_chaman_tera_notes</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Trumpet</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Trumpet Notes</v>
+      </c>
+      <c r="E2" t="str">
+        <v>burhandeen_chaman_tera_notes.pdf</v>
+      </c>
+      <c r="F2" t="str">
+        <v>/uploads/tunes/Trumpet%20Notes/1790366817660_burhandeen_chaman_tera_notes.pdf</v>
+      </c>
+      <c r="G2" t="str">
+        <v>https://www.youtube.com/watch?v=QM1UC7O0sWI</v>
+      </c>
+      <c r="H2" t="str">
+        <v/>
+      </c>
+      <c r="I2" t="str">
+        <v>MUFADDAL ABIZARBHAI VALINABU (Major)</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:I2"/>
+  </ignoredErrors>
+</worksheet>
 </file>
--- a/src/data/TAHERI_SCOUT_BAND_GROUP_1448H.xlsx
+++ b/src/data/TAHERI_SCOUT_BAND_GROUP_1448H.xlsx
@@ -9,6 +9,7 @@
     <sheet name="Lavajam Details" sheetId="4" r:id="rId4"/>
     <sheet name="Instrument Expenses" sheetId="5" r:id="rId5"/>
     <sheet name="Reference Link" sheetId="6" r:id="rId6"/>
+    <sheet name="Assign Notes" sheetId="7" r:id="rId7"/>
   </sheets>
 </workbook>
 </file>
@@ -3748,7 +3749,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:D5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3760,43 +3761,69 @@
       <c r="C1" t="str">
         <v>Amount</v>
       </c>
+      <c r="D1" t="str">
+        <v>Additional Notes</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>24/09/2026</v>
+        <v>27/09/2026</v>
       </c>
       <c r="B2" t="str">
-        <v>Instument purchase</v>
+        <v>Test</v>
       </c>
       <c r="C2">
-        <v>20500</v>
+        <v>1000</v>
+      </c>
+      <c r="D2" t="str">
+        <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>24/09/2026</v>
+        <v>20/09/2026</v>
       </c>
       <c r="B3" t="str">
-        <v>Baner express</v>
+        <v>Instument purchase</v>
       </c>
       <c r="C3">
-        <v>2500</v>
+        <v>21000</v>
+      </c>
+      <c r="D3" t="str">
+        <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>24/09/2026</v>
+        <v>20/09/2026</v>
       </c>
       <c r="B4" t="str">
+        <v>Baner express</v>
+      </c>
+      <c r="C4">
+        <v>2500</v>
+      </c>
+      <c r="D4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>20/09/2026</v>
+      </c>
+      <c r="B5" t="str">
         <v>Instument purchase</v>
       </c>
-      <c r="C4">
+      <c r="C5">
         <v>1370</v>
+      </c>
+      <c r="D5" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D5"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3836,10 +3863,10 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2026-09-25T20:06:57.662Z</v>
+        <v>2026-09-26T18:38:03.927Z</v>
       </c>
       <c r="B2" t="str">
-        <v>burhandeen_chaman_tera_notes</v>
+        <v>C Scale Learning Notes</v>
       </c>
       <c r="C2" t="str">
         <v>Trumpet</v>
@@ -3848,19 +3875,19 @@
         <v>Trumpet Notes</v>
       </c>
       <c r="E2" t="str">
-        <v>burhandeen_chaman_tera_notes.pdf</v>
+        <v>C scale notes.pdf</v>
       </c>
       <c r="F2" t="str">
-        <v>/uploads/tunes/Trumpet%20Notes/1790366817660_burhandeen_chaman_tera_notes.pdf</v>
+        <v>/uploads/tunes/Trumpet%20Notes/1790447883911_C_scale_notes.pdf</v>
       </c>
       <c r="G2" t="str">
-        <v>https://www.youtube.com/watch?v=QM1UC7O0sWI</v>
+        <v/>
       </c>
       <c r="H2" t="str">
         <v/>
       </c>
       <c r="I2" t="str">
-        <v>MUFADDAL ABIZARBHAI VALINABU (Major)</v>
+        <v>BURHAN JUZARBHAI KUNDAWALA (Trumpet Major)</v>
       </c>
     </row>
   </sheetData>
@@ -3868,4 +3895,66 @@
     <ignoredError numberStoredAsText="1" sqref="A1:I2"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E3"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Member Name</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Assigned Tunes</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Section</v>
+      </c>
+      <c r="D1" t="str">
+        <v>ITS Number</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Last Updated</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>BURHAN JUZARBHAI KUNDAWALA</v>
+      </c>
+      <c r="B2" t="str">
+        <v>burhandeen_chaman_tera_notes, hai_tahani_al_maula_notes</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Trumpet</v>
+      </c>
+      <c r="D2" t="str">
+        <v>40405600</v>
+      </c>
+      <c r="E2" t="str">
+        <v>2026-09-27T11:00:24.358Z</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>TAHER AKBARBHAI MANDSORWALA</v>
+      </c>
+      <c r="B3" t="str">
+        <v>C Scale Learning Notes</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Trumpet</v>
+      </c>
+      <c r="D3" t="str">
+        <v>40404863</v>
+      </c>
+      <c r="E3" t="str">
+        <v>2026-09-27T11:00:24.358Z</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:E3"/>
+  </ignoredErrors>
+</worksheet>
 </file>
--- a/src/data/TAHERI_SCOUT_BAND_GROUP_1448H.xlsx
+++ b/src/data/TAHERI_SCOUT_BAND_GROUP_1448H.xlsx
@@ -1544,7 +1544,7 @@
         <v>40915293</v>
       </c>
       <c r="C40" t="str">
-        <v>ALIASGAR MUFADDAL KANCHWALA</v>
+        <v>ALIASGAR MUFADDALBHAI KANCHWALA</v>
       </c>
       <c r="D40" t="str">
         <v>Idries manjil 3rd floor noor baugh</v>
@@ -1556,7 +1556,7 @@
         <v>SHUJAI SECTOR</v>
       </c>
       <c r="G40" t="str">
-        <v>Trumpet Member</v>
+        <v>Ghugara Member</v>
       </c>
       <c r="H40" t="str">
         <v>aliasgarKanchwala@tsgband.com</v>
@@ -2744,7 +2744,7 @@
         <v>40915293</v>
       </c>
       <c r="C40" t="str">
-        <v>ALIASGAR MUFADDAL KANCHWALA</v>
+        <v>ALIASGAR MUFADDALBHAI KANCHWALA</v>
       </c>
       <c r="D40" t="str">
         <v>Idries manjil 3rd floor noor baugh</v>
@@ -2756,7 +2756,7 @@
         <v>SHUJAI SECTOR</v>
       </c>
       <c r="G40" t="str">
-        <v>Trumpet Member</v>
+        <v>Ghugara Member</v>
       </c>
       <c r="H40" t="str">
         <v>aliasgarKanchwala@tsgband.com</v>
@@ -3236,7 +3236,7 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>ALIASGAR MUFADDAL KANCHWALA</v>
+        <v>ALIASGAR MUFADDALBHAI KANCHWALA</v>
       </c>
       <c r="B40" t="str">
         <v/>
@@ -3676,7 +3676,7 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>ALIASGAR MUFADDAL KANCHWALA</v>
+        <v>ALIASGAR MUFADDALBHAI KANCHWALA</v>
       </c>
       <c r="B38" t="str">
         <v>Lavajam</v>

--- a/src/data/TAHERI_SCOUT_BAND_GROUP_1448H.xlsx
+++ b/src/data/TAHERI_SCOUT_BAND_GROUP_1448H.xlsx
@@ -3830,7 +3830,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3890,9 +3890,38 @@
         <v>BURHAN JUZARBHAI KUNDAWALA (Trumpet Major)</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>2026-09-29T12:26:22.191Z</v>
+      </c>
+      <c r="B3" t="str">
+        <v>AQA Moula Tune</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Trumpet</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Trumpet Notes</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Aqa Moula Converted.pdf</v>
+      </c>
+      <c r="F3" t="str">
+        <v>/uploads/tunes/Trumpet%20Notes/1790684782183_Aqa_Moula_Converted.pdf</v>
+      </c>
+      <c r="G3" t="str">
+        <v>https://www.youtube.com/watch?v=fRhv0VRICr0</v>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>BURHAN JUZARBHAI KUNDAWALA (Trumpet Major)</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I3"/>
   </ignoredErrors>
 </worksheet>
 </file>
